--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_18.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_18.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ExamGrade</t>
+          <t>RiskTaking</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Interesting</t>
+          <t>InformationLevel</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9109233891621036</v>
+        <v>-0.2989012718809057</v>
       </c>
       <c r="C2">
-        <v>0.5886107578048648</v>
+        <v>0.2974200105519789</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.4855614789189164</v>
+        <v>-0.1718669217413732</v>
       </c>
       <c r="C3">
-        <v>0.1679830394334778</v>
+        <v>0.6236760021701615</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-1.034531825958928</v>
+        <v>-0.1241553779450028</v>
       </c>
       <c r="C4">
-        <v>-0.4629002070087794</v>
+        <v>2.711384733055105</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.202443855147083</v>
+        <v>-0.1011255291621543</v>
       </c>
       <c r="C5">
-        <v>-0.8415415570929804</v>
+        <v>-0.3984476695280993</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.8188512331271209</v>
+        <v>-0.07119902723538295</v>
       </c>
       <c r="C6">
-        <v>-0.151720771146315</v>
+        <v>-0.07898974335935967</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.1162422031378113</v>
+        <v>0.7206072512125027</v>
       </c>
       <c r="C7">
-        <v>-1.165806042998071</v>
+        <v>0.1631304251119649</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.6642621483274251</v>
+        <v>0.1158733043145551</v>
       </c>
       <c r="C8">
-        <v>0.4011727738866208</v>
+        <v>-0.4551822440436989</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.5466392195146677</v>
+        <v>0.7619234579855408</v>
       </c>
       <c r="C9">
-        <v>0.2111207601885192</v>
+        <v>-0.9691168206051608</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.3739483898827262</v>
+        <v>0.03811833846905148</v>
       </c>
       <c r="C10">
-        <v>0.7244779146131084</v>
+        <v>0.8136438967836791</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-1.441500409469097</v>
+        <v>-0.2179081573072287</v>
       </c>
       <c r="C11">
-        <v>-3.102301961828014</v>
+        <v>0.8959243376254244</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.3853266898628973</v>
+        <v>0.9959662116927825</v>
       </c>
       <c r="C12">
-        <v>0.8499932839912274</v>
+        <v>-1.110846669549602</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.245814230673367</v>
+        <v>1.577161259221995</v>
       </c>
       <c r="C13">
-        <v>-0.5680571227889377</v>
+        <v>-0.3694320477018121</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.3082549818074468</v>
+        <v>1.861949460769684</v>
       </c>
       <c r="C14">
-        <v>-0.2062701794899761</v>
+        <v>0.09169999724029598</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.2342204407844327</v>
+        <v>1.573671833620116</v>
       </c>
       <c r="C15">
-        <v>1.139461959098235</v>
+        <v>1.859979815081451</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.03930370756253049</v>
+        <v>-1.970950594828102</v>
       </c>
       <c r="C16">
-        <v>-0.721231690936283</v>
+        <v>-1.850873688334875</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.1073406111854533</v>
+        <v>-1.120111362720311</v>
       </c>
       <c r="C17">
-        <v>-1.217789423706277</v>
+        <v>-0.4420256500002316</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-1.927366212083155</v>
+        <v>-1.387391364947659</v>
       </c>
       <c r="C18">
-        <v>0.8938069073237589</v>
+        <v>0.3209317698294926</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-1.362372385228492</v>
+        <v>0.01176491364919787</v>
       </c>
       <c r="C19">
-        <v>-0.7983056880326478</v>
+        <v>2.0978755067648</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.8482280304635198</v>
+        <v>0.3283824986596717</v>
       </c>
       <c r="C20">
-        <v>-1.678076777921052</v>
+        <v>-0.8900279567064964</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.7031792175245958</v>
+        <v>-0.5467765580127264</v>
       </c>
       <c r="C21">
-        <v>0.1399461268910313</v>
+        <v>0.2887630249637109</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.5069513448851792</v>
+        <v>0.4297720165806865</v>
       </c>
       <c r="C22">
-        <v>-0.5719056864850937</v>
+        <v>0.8813548574876418</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-1.678963350699941</v>
+        <v>0.8530885143088518</v>
       </c>
       <c r="C23">
-        <v>-0.3780705990147855</v>
+        <v>2.046405468974686</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.7142971891526561</v>
+        <v>0.6455867540292142</v>
       </c>
       <c r="C24">
-        <v>0.7499285653925942</v>
+        <v>1.730082380571036</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.6180066834989507</v>
+        <v>-0.9853123999906909</v>
       </c>
       <c r="C25">
-        <v>-1.514216524881227</v>
+        <v>-0.6436965858203837</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.1587984842773725</v>
+        <v>-0.1870252598016927</v>
       </c>
       <c r="C26">
-        <v>-0.04345444529267369</v>
+        <v>-0.04263104843686878</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.8185632132429399</v>
+        <v>-0.5790620914299623</v>
       </c>
       <c r="C27">
-        <v>1.596911311831564</v>
+        <v>-1.670627607710204</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.038719864960811</v>
+        <v>-0.4616123765122133</v>
       </c>
       <c r="C28">
-        <v>1.220343917978137</v>
+        <v>1.440890742670824</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.6446179498244522</v>
+        <v>-0.04762758629733242</v>
       </c>
       <c r="C29">
-        <v>0.7356288233214593</v>
+        <v>-0.4127333827199081</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-1.276807645823693</v>
+        <v>0.5339801159068996</v>
       </c>
       <c r="C30">
-        <v>-2.925452854599917</v>
+        <v>0.3853929762611563</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.6859866471009664</v>
+        <v>1.826795758073932</v>
       </c>
       <c r="C31">
-        <v>0.6306743353672746</v>
+        <v>2.282921296418043</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.3682847506824869</v>
+        <v>-0.6786806239282863</v>
       </c>
       <c r="C32">
-        <v>0.4634312968297898</v>
+        <v>0.3439626960506418</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.310617571792958</v>
+        <v>0.2444741012215915</v>
       </c>
       <c r="C33">
-        <v>0.7578203234941365</v>
+        <v>1.017424039512934</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-2.198470076638638</v>
+        <v>-1.477911759677627</v>
       </c>
       <c r="C34">
-        <v>-0.763584763140661</v>
+        <v>-1.179892115474555</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>1.968627175388605</v>
+        <v>-0.4691297523956385</v>
       </c>
       <c r="C35">
-        <v>-0.1695128208777171</v>
+        <v>0.8195426896824868</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.6133520946505222</v>
+        <v>-0.4296660917458153</v>
       </c>
       <c r="C36">
-        <v>-0.5637411999415106</v>
+        <v>1.258781369972763</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.8489855636022343</v>
+        <v>0.1957095160402221</v>
       </c>
       <c r="C37">
-        <v>-0.6150586468589072</v>
+        <v>0.398763774987489</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.06734532579531936</v>
+        <v>1.058832517185603</v>
       </c>
       <c r="C38">
-        <v>-0.1583816137062029</v>
+        <v>0.1121736556555719</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.5878834571498041</v>
+        <v>-0.09632359859578332</v>
       </c>
       <c r="C39">
-        <v>-0.3728282920194276</v>
+        <v>-2.832630262214099</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.702162823120064</v>
+        <v>-0.5979251892310971</v>
       </c>
       <c r="C40">
-        <v>-0.5700980111737699</v>
+        <v>1.265054497591936</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.5958593539893187</v>
+        <v>-0.7451325799694427</v>
       </c>
       <c r="C41">
-        <v>0.8880724741673778</v>
+        <v>-1.618222863186816</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.3871098989454382</v>
+        <v>0.9529975263830838</v>
       </c>
       <c r="C42">
-        <v>-0.03887137358270329</v>
+        <v>2.164744453996288</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.2081859089724541</v>
+        <v>-0.04003885263045982</v>
       </c>
       <c r="C43">
-        <v>1.089945928045001</v>
+        <v>-0.715585584180782</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.476922012638504</v>
+        <v>0.986121413059134</v>
       </c>
       <c r="C44">
-        <v>1.107372564680484</v>
+        <v>-0.06321089651124912</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.4225072034055884</v>
+        <v>-1.574439010295374</v>
       </c>
       <c r="C45">
-        <v>-0.1425981821366394</v>
+        <v>-1.853268775686171</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.1081771779767296</v>
+        <v>1.158822285870943</v>
       </c>
       <c r="C46">
-        <v>-1.169946638993359</v>
+        <v>1.606317330246186</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.7955320784001694</v>
+        <v>-1.631722491919215</v>
       </c>
       <c r="C47">
-        <v>-1.65639467072244</v>
+        <v>-0.0812063080565979</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.01186312073280207</v>
+        <v>1.506204631785606</v>
       </c>
       <c r="C48">
-        <v>0.5123081846087274</v>
+        <v>-0.3419251008509558</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>1.077490046853601</v>
+        <v>-1.961337531342899</v>
       </c>
       <c r="C49">
-        <v>-1.088808876443018</v>
+        <v>-0.4753445275656962</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.6370521109843525</v>
+        <v>0.8671776229901539</v>
       </c>
       <c r="C50">
-        <v>-0.5057374223612234</v>
+        <v>1.040074599382121</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.3584778512479799</v>
+        <v>-0.2915865051034684</v>
       </c>
       <c r="C51">
-        <v>0.5005767255629486</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>-0.02701482352265278</v>
-      </c>
-      <c r="C52">
-        <v>-0.9603380838904688</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>-0.556475814813742</v>
-      </c>
-      <c r="C53">
-        <v>1.673864172071968</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>-0.2624323318403698</v>
-      </c>
-      <c r="C54">
-        <v>0.2650697538499941</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>-1.587832091976475</v>
-      </c>
-      <c r="C55">
-        <v>0.7549137120868237</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>0.03538901220302025</v>
-      </c>
-      <c r="C56">
-        <v>0.4601002946299238</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>0.9847996798895456</v>
-      </c>
-      <c r="C57">
-        <v>-1.221413398160087</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>-0.6253466558783106</v>
-      </c>
-      <c r="C58">
-        <v>0.4365720159122524</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>-0.1988525863495261</v>
-      </c>
-      <c r="C59">
-        <v>-0.8355487290197924</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>-0.9679250075527207</v>
-      </c>
-      <c r="C60">
-        <v>-0.197898302006399</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>-0.6254537811129381</v>
-      </c>
-      <c r="C61">
-        <v>-0.3157527835270553</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>0.657370707785489</v>
-      </c>
-      <c r="C62">
-        <v>0.3888417258679548</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>1.448457433313824</v>
-      </c>
-      <c r="C63">
-        <v>1.249748277835488</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>0.3212372862384172</v>
-      </c>
-      <c r="C64">
-        <v>-1.519883964450969</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>0.424655245602231</v>
-      </c>
-      <c r="C65">
-        <v>0.5643344776009345</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>-0.6553051131019207</v>
-      </c>
-      <c r="C66">
-        <v>-1.964311079960912</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>1.071505028288728</v>
-      </c>
-      <c r="C67">
-        <v>0.03315729450942057</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>-1.212482581925961</v>
-      </c>
-      <c r="C68">
-        <v>-0.1316823371821887</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>-2.528100464258158</v>
-      </c>
-      <c r="C69">
-        <v>-0.231775735721653</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>-0.9801161818832198</v>
-      </c>
-      <c r="C70">
-        <v>-0.6817959158603712</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>-0.4546185876494692</v>
-      </c>
-      <c r="C71">
-        <v>-2.746485278311692</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>-0.3981583631916563</v>
-      </c>
-      <c r="C72">
-        <v>-0.7187052491886929</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>0.8721380156036622</v>
-      </c>
-      <c r="C73">
-        <v>-1.730654946282444</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>-0.8044578773682052</v>
-      </c>
-      <c r="C74">
-        <v>-0.4035370036258559</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>0.08218593947931871</v>
-      </c>
-      <c r="C75">
-        <v>1.968512238896376</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>1.425258562300351</v>
-      </c>
-      <c r="C76">
-        <v>0.6318617912838053</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>0.251775965156084</v>
-      </c>
-      <c r="C77">
-        <v>-1.340415799448945</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>0.5116991818259671</v>
-      </c>
-      <c r="C78">
-        <v>1.099021791594686</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>0.6339707549601843</v>
-      </c>
-      <c r="C79">
-        <v>0.5731770765282025</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>-0.2977477133670696</v>
-      </c>
-      <c r="C80">
-        <v>-1.081273554949515</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>-0.6909592214403544</v>
-      </c>
-      <c r="C81">
-        <v>-1.926803475554009</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>0.5568738924091784</v>
-      </c>
-      <c r="C82">
-        <v>0.3171193257487549</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>0.4840945087979346</v>
-      </c>
-      <c r="C83">
-        <v>-1.12709692298171</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>0.0230008798971785</v>
-      </c>
-      <c r="C84">
-        <v>0.03581846167871194</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>-0.1170589256860764</v>
-      </c>
-      <c r="C85">
-        <v>0.3770913450903917</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>0.4027072130448414</v>
-      </c>
-      <c r="C86">
-        <v>0.8045290915744782</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>1.512872102550176</v>
-      </c>
-      <c r="C87">
-        <v>1.207060090212157</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>-0.4484193713230832</v>
-      </c>
-      <c r="C88">
-        <v>0.9620768838032776</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>0.2068417427517865</v>
-      </c>
-      <c r="C89">
-        <v>-0.3211770185005838</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>0.7512952396424237</v>
-      </c>
-      <c r="C90">
-        <v>-0.09271455269567014</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>-0.4310019169298435</v>
-      </c>
-      <c r="C91">
-        <v>-0.1113246170212327</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>-1.888146618841619</v>
-      </c>
-      <c r="C92">
-        <v>-0.2578771475472859</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>-1.463725958822781</v>
-      </c>
-      <c r="C93">
-        <v>-0.7383278668601061</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>0.973609638648117</v>
-      </c>
-      <c r="C94">
-        <v>1.493125394654368</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>-1.130766027750209</v>
-      </c>
-      <c r="C95">
-        <v>0.515740594913239</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>-0.2584124523826108</v>
-      </c>
-      <c r="C96">
-        <v>0.6075200780138167</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>-0.4527246217246448</v>
-      </c>
-      <c r="C97">
-        <v>-1.582100148127591</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>0.3690909535069432</v>
-      </c>
-      <c r="C98">
-        <v>1.312965437397639</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>-1.269927472408768</v>
-      </c>
-      <c r="C99">
-        <v>-1.03807921908425</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>0.4324178742073471</v>
-      </c>
-      <c r="C100">
-        <v>1.146122383580806</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>0.5625825319004134</v>
-      </c>
-      <c r="C101">
-        <v>-0.5551468765110532</v>
+        <v>-0.743591335853774</v>
       </c>
     </row>
   </sheetData>
